--- a/src/main/resources/Logs/cargaMasivaLog.xlsx
+++ b/src/main/resources/Logs/cargaMasivaLog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService\src\main\resources\Logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CA341F7-65C0-4F36-A310-CA7849FAA0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB310DB-8515-4EE7-A32E-FECC0C4FB78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,28 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Accion</t>
-  </si>
-  <si>
-    <t>Archivo</t>
-  </si>
-  <si>
-    <t>FechaHora</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Token</t>
-  </si>
-  <si>
-    <t>Mensaje</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="250">
   <si>
     <t>SUBIR</t>
   </si>
@@ -104,6 +83,694 @@
   </si>
   <si>
     <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251126183381cargat2.txt</t>
+  </si>
+  <si>
+    <t>20251218124967cargat2.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 12:49:55</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218124966cargat2.txt</t>
+  </si>
+  <si>
+    <t>VALIDAR</t>
+  </si>
+  <si>
+    <t>20251218124966cargat2.txt</t>
+  </si>
+  <si>
+    <t>VALIDADO</t>
+  </si>
+  <si>
+    <t>67e261f7-0f21-4d63-afbc-a0e7445c2d18</t>
+  </si>
+  <si>
+    <t>Validación correcta</t>
+  </si>
+  <si>
+    <t>20251218125729CargaMasiva2.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 12:57:55</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218125729CargaMasiva2.xlsx</t>
+  </si>
+  <si>
+    <t>0f09ec13-a757-45dd-a716-e8a264ccbc45</t>
+  </si>
+  <si>
+    <t>20251218130618CargaMasiva2.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:06:47</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218130618CargaMasiva2.xlsx</t>
+  </si>
+  <si>
+    <t>34b2edd8-164c-4352-9308-7687a40f245e</t>
+  </si>
+  <si>
+    <t>20251218130851cargat2.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:08:08</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218130851cargat2.txt</t>
+  </si>
+  <si>
+    <t>7da80d35-389d-41d0-8188-202b5f111111</t>
+  </si>
+  <si>
+    <t>20251218131395cargat2.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:13:39</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218131395cargat2.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:13:40</t>
+  </si>
+  <si>
+    <t>ERROR_VALIDACION</t>
+  </si>
+  <si>
+    <t>Error al leer el archivo</t>
+  </si>
+  <si>
+    <t>20251218131645cargat2.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:16:35</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218131645cargat2.txt</t>
+  </si>
+  <si>
+    <t>20251218132441cargat2.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:24:08</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218132441cargat2.txt</t>
+  </si>
+  <si>
+    <t>19753412-93a5-4745-8407-e152376297a6</t>
+  </si>
+  <si>
+    <t>20251218133083cargat2.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:30:01</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218133082cargat2.txt</t>
+  </si>
+  <si>
+    <t>20251218133082cargat2.txt</t>
+  </si>
+  <si>
+    <t>aa69b745-fbe9-443d-a0f4-7b63827dcb4e</t>
+  </si>
+  <si>
+    <t>20251218133540cargat2.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:35:22</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218133539cargat2.txt</t>
+  </si>
+  <si>
+    <t>20251218133539cargat2.txt</t>
+  </si>
+  <si>
+    <t>a8d894c1-c4ce-4c1b-9c7f-3fadde7624ab</t>
+  </si>
+  <si>
+    <t>20251218133888CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:38:10</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218133887CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>20251218133887CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 13:38:11</t>
+  </si>
+  <si>
+    <t>85796d4d-6e7c-4e48-bf46-3dc3f1f7c7af</t>
+  </si>
+  <si>
+    <t>20251218140158CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:01:12</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218140158CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>b3679970-97c0-4633-928b-f2b07f5f05bd</t>
+  </si>
+  <si>
+    <t>20251218140141CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:01:50</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218140141CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>5fbb7656-1b3c-4fa0-8f29-6352a4d1301d</t>
+  </si>
+  <si>
+    <t>20251218141668CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:16:26</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218141668CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:16:27</t>
+  </si>
+  <si>
+    <t>Se encontraron errores en los datos</t>
+  </si>
+  <si>
+    <t>20251218141774cargat2.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:17:12</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218141773cargat2.txt</t>
+  </si>
+  <si>
+    <t>20251218141773cargat2.txt</t>
+  </si>
+  <si>
+    <t>335edfee-9335-407a-93ff-130866877900</t>
+  </si>
+  <si>
+    <t>20251218142200CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:22:58</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218142200CargaConErrores.txt</t>
+  </si>
+  <si>
+    <t>20251218142378CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:23:09</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218142378CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>70738539-762f-4475-a218-a40d9cb7f75f</t>
+  </si>
+  <si>
+    <t>20251218142353CargaConErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:23:23</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218142353CargaConErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218142364CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:23:42</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218142364CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218142462CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:24:00</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218142461CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218142461CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218142473CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:24:54</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218142473CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218142911CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:29:54</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218142911CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218143054CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:30:12</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218143054CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218143010CargaConErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:30:24</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218143009CargaConErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218143009CargaConErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218143468CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:34:05</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218143468CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>636e7104-3988-4c1a-93ab-d6dc996dd37f</t>
+  </si>
+  <si>
+    <t>20251218143402CargaConErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:34:17</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218143402CargaConErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251218143445CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-18 14:34:29</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251218143445CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>0a1e3e29-6076-4f09-94f6-c9ddde2690a1</t>
+  </si>
+  <si>
+    <t>20251222102881CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 10:28:18</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222102880CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251222102880CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>662eacb1-fa70-4a54-a9db-3f9a20957fde</t>
+  </si>
+  <si>
+    <t>2025-12-22 10:30:18</t>
+  </si>
+  <si>
+    <t>20251222103373CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 10:33:05</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222103373CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>71e7c552-a260-42a7-8177-1ee26b70fa98</t>
+  </si>
+  <si>
+    <t>2025-12-22 10:35:05</t>
+  </si>
+  <si>
+    <t>20251222110882CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:08:19</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222110881CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251222110881CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:08:20</t>
+  </si>
+  <si>
+    <t>58b77d79-b018-4501-aaba-fadee5c35dc2</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:10:20</t>
+  </si>
+  <si>
+    <t>20251222111274CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:12:00</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222111274CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>87cab8cb-2435-4f33-b30f-27726d005391</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:14:00</t>
+  </si>
+  <si>
+    <t>20251222112233CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:22:04</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222112233CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>4a6c59dd-bfec-4bdb-a939-4c72b94eabd5</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:24:04</t>
+  </si>
+  <si>
+    <t>20251222112251CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:22:31</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222112251CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>6509a970-ec6e-4d80-8672-9d22c684392f</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:24:31</t>
+  </si>
+  <si>
+    <t>20251222112309CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:23:32</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222112309CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>a0b488b7-db4a-4f16-93f0-4d4371e423e3</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:25:32</t>
+  </si>
+  <si>
+    <t>20251222113422CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:34:38</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222113422CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>67ea19db-26ac-4744-9482-47411bcb3f54</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:36:38</t>
+  </si>
+  <si>
+    <t>PROCESAR</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:34:42</t>
+  </si>
+  <si>
+    <t>ERROR_TOKEN</t>
+  </si>
+  <si>
+    <t>Token inválido o expirado</t>
+  </si>
+  <si>
+    <t>20251222115543CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:55:22</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222115542CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>20251222115542CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:55:23</t>
+  </si>
+  <si>
+    <t>20e80bbe-1c18-4a86-bf40-49c23059b8b3</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:57:23</t>
+  </si>
+  <si>
+    <t>2025-12-22 11:56:39</t>
+  </si>
+  <si>
+    <t>20251222121228CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 12:12:19</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor: C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222121228CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>6294797d-059d-4a49-938f-ba06c6784386</t>
+  </si>
+  <si>
+    <t>2025-12-22 12:14:19</t>
+  </si>
+  <si>
+    <t>Archivo validado correctamente</t>
+  </si>
+  <si>
+    <t>2025-12-22 12:12:32</t>
+  </si>
+  <si>
+    <t>ERROR_PROCESO</t>
+  </si>
+  <si>
+    <t>El archivo no existe: Archivo validado correctamente</t>
+  </si>
+  <si>
+    <t>idLog</t>
+  </si>
+  <si>
+    <t>accion</t>
+  </si>
+  <si>
+    <t>nombreArchivo</t>
+  </si>
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>token</t>
+  </si>
+  <si>
+    <t>expira</t>
+  </si>
+  <si>
+    <t>rutaArchivo</t>
+  </si>
+  <si>
+    <t>mensaje</t>
+  </si>
+  <si>
+    <t>20251222133138CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>2025-12-22 13:31:51</t>
+  </si>
+  <si>
+    <t>C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251222133137CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>Archivo almacenado en el servidor</t>
+  </si>
+  <si>
+    <t>20251222133137CargaSinErroresEx.xlsx</t>
+  </si>
+  <si>
+    <t>cf74f1b9-dda1-4666-b805-c0b55eb454d0</t>
+  </si>
+  <si>
+    <t>2025-12-22 13:33:51</t>
+  </si>
+  <si>
+    <t>2025-12-22 13:32:42</t>
+  </si>
+  <si>
+    <t>2025-12-22 13:34:42</t>
+  </si>
+  <si>
+    <t>20251223100683CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:06:25</t>
+  </si>
+  <si>
+    <t>C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251223100682CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>20251223100682CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>ce9d5886-e35f-4262-9901-30632277a3b2</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:08:25</t>
+  </si>
+  <si>
+    <t>20251223100637CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:06:57</t>
+  </si>
+  <si>
+    <t>C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251223100637CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>494124e1-357a-47f5-8dcd-a39cced00767</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:08:57</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:08:48</t>
+  </si>
+  <si>
+    <t>could not execute statement [ORA-00001: unique constraint (CMONROYPROGRAMACIONNCAPAS.SYS_C009896) violated
+https://docs.oracle.com/error-help/db/ora-00001/] [insert into usuario (apellidomaterno,apellidopaterno,celular,curp,email,fechanacimiento,isverified,nombre,password,idrol,sexo,status,telefono,verificationtoken,username,idusuario,imagen) values (?,?,?,?,?,?,?,?,?,?,?,?,?,?,?,default,?)]; SQL [insert into usuario (apellidomaterno,apellidopaterno,celular,curp,email,fechanacimiento,isverified,nombre,password,idrol,sexo,status,telefono,verificationtoken,username,idusuario,imagen) values (?,?,?,?,?,?,?,?,?,?,?,?,?,?,?,default,?)]; constraint [CMONROYPROGRAMACIONNCAPAS.SYS_C009896]</t>
+  </si>
+  <si>
+    <t>20251223101172CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:11:41</t>
+  </si>
+  <si>
+    <t>C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251223101172CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>1f180766-145a-46d8-a1d0-13da7514ea1f</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:13:41</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:13:09</t>
+  </si>
+  <si>
+    <t>20251223101541CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:15:16</t>
+  </si>
+  <si>
+    <t>C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251223101541CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>bcf9fad5-a2bf-4e95-a46a-9e6e02a81ede</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:17:16</t>
+  </si>
+  <si>
+    <t>20251223101638CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:16:08</t>
+  </si>
+  <si>
+    <t>C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251223101638CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>6a561790-6da6-4f8d-85f5-c8ae264d2dc1</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:18:08</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:18:04</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:20:04</t>
+  </si>
+  <si>
+    <t>20251223102308CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:23:13</t>
+  </si>
+  <si>
+    <t>C:\Users\digis\OneDrive\Documentos\Christian Manuel Monroy Patiño\com.digi01_CMonroyProgramacionNCapasSpringService/src/main/resources/archivosCarga/20251223102307CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>20251223102307CargaSinErrores.txt</t>
+  </si>
+  <si>
+    <t>17416e2a-1602-4f55-b624-0f5f9fcee76f</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:25:13</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:23:42</t>
+  </si>
+  <si>
+    <t>2025-12-23 10:25:42</t>
   </si>
 </sst>
 </file>
@@ -422,168 +1089,2522 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="34.6640625" collapsed="true"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="B1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
+      <c r="B26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" t="s">
+        <v>73</v>
+      </c>
+      <c r="G29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" t="s">
+        <v>87</v>
+      </c>
+      <c r="G35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" t="s">
+        <v>99</v>
+      </c>
+      <c r="E42" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" t="s">
+        <v>102</v>
+      </c>
+      <c r="E45" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" t="s">
+        <v>106</v>
+      </c>
+      <c r="E47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" t="s">
+        <v>109</v>
+      </c>
+      <c r="E48" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" t="s">
+        <v>109</v>
+      </c>
+      <c r="E49" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" t="s">
+        <v>112</v>
+      </c>
+      <c r="E50" t="s">
+        <v>3</v>
+      </c>
+      <c r="F50" t="s">
+        <v>4</v>
+      </c>
+      <c r="G50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F51" t="s">
+        <v>4</v>
+      </c>
+      <c r="G51" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D53" t="s">
+        <v>115</v>
+      </c>
+      <c r="E53" t="s">
+        <v>45</v>
+      </c>
+      <c r="F53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G53" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" t="s">
+        <v>119</v>
+      </c>
+      <c r="E54" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55" t="s">
+        <v>119</v>
+      </c>
+      <c r="E55" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55" t="s">
+        <v>121</v>
+      </c>
+      <c r="G55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" t="s">
+        <v>123</v>
+      </c>
+      <c r="E56" t="s">
+        <v>3</v>
+      </c>
+      <c r="F56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>122</v>
+      </c>
+      <c r="D57" t="s">
+        <v>123</v>
+      </c>
+      <c r="E57" t="s">
+        <v>45</v>
+      </c>
+      <c r="F57" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" t="s">
+        <v>125</v>
+      </c>
+      <c r="D58" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" t="s">
+        <v>126</v>
+      </c>
+      <c r="E59" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" t="s">
+        <v>128</v>
+      </c>
+      <c r="G59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" t="s">
+        <v>129</v>
+      </c>
+      <c r="D60" t="s">
+        <v>130</v>
+      </c>
+      <c r="E60" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" t="s">
+        <v>132</v>
+      </c>
+      <c r="D61" t="s">
+        <v>130</v>
+      </c>
+      <c r="E61" t="s">
+        <v>26</v>
+      </c>
+      <c r="F61" t="s">
+        <v>133</v>
+      </c>
+      <c r="G61" t="s">
+        <v>134</v>
+      </c>
+      <c r="H61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" t="s">
+        <v>135</v>
+      </c>
+      <c r="D62" t="s">
+        <v>136</v>
+      </c>
+      <c r="E62" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" t="s">
+        <v>136</v>
+      </c>
+      <c r="E63" t="s">
+        <v>26</v>
+      </c>
+      <c r="F63" t="s">
+        <v>138</v>
+      </c>
+      <c r="G63" t="s">
+        <v>139</v>
+      </c>
+      <c r="H63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C64" t="s">
+        <v>140</v>
+      </c>
+      <c r="D64" t="s">
+        <v>141</v>
+      </c>
+      <c r="E64" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" t="s">
+        <v>4</v>
+      </c>
+      <c r="G64" t="s">
+        <v>4</v>
+      </c>
+      <c r="H64" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>143</v>
+      </c>
+      <c r="D65" t="s">
+        <v>144</v>
+      </c>
+      <c r="E65" t="s">
+        <v>26</v>
+      </c>
+      <c r="F65" t="s">
+        <v>145</v>
+      </c>
+      <c r="G65" t="s">
+        <v>146</v>
+      </c>
+      <c r="H65" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" t="s">
+        <v>148</v>
+      </c>
+      <c r="E66" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>147</v>
+      </c>
+      <c r="D67" t="s">
+        <v>148</v>
+      </c>
+      <c r="E67" t="s">
+        <v>26</v>
+      </c>
+      <c r="F67" t="s">
+        <v>150</v>
+      </c>
+      <c r="G67" t="s">
+        <v>151</v>
+      </c>
+      <c r="H67" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>0</v>
+      </c>
+      <c r="C68" t="s">
+        <v>152</v>
+      </c>
+      <c r="D68" t="s">
+        <v>153</v>
+      </c>
+      <c r="E68" t="s">
+        <v>3</v>
+      </c>
+      <c r="F68" t="s">
+        <v>4</v>
+      </c>
+      <c r="G68" t="s">
+        <v>4</v>
+      </c>
+      <c r="H68" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>152</v>
+      </c>
+      <c r="D69" t="s">
+        <v>153</v>
+      </c>
+      <c r="E69" t="s">
+        <v>26</v>
+      </c>
+      <c r="F69" t="s">
+        <v>155</v>
+      </c>
+      <c r="G69" t="s">
+        <v>156</v>
+      </c>
+      <c r="H69" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>0</v>
+      </c>
+      <c r="C70" t="s">
+        <v>157</v>
+      </c>
+      <c r="D70" t="s">
+        <v>158</v>
+      </c>
+      <c r="E70" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" t="s">
+        <v>4</v>
+      </c>
+      <c r="G70" t="s">
+        <v>4</v>
+      </c>
+      <c r="H70" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" t="s">
+        <v>158</v>
+      </c>
+      <c r="E71" t="s">
+        <v>26</v>
+      </c>
+      <c r="F71" t="s">
+        <v>160</v>
+      </c>
+      <c r="G71" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>0</v>
+      </c>
+      <c r="C72" t="s">
+        <v>162</v>
+      </c>
+      <c r="D72" t="s">
+        <v>163</v>
+      </c>
+      <c r="E72" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>162</v>
+      </c>
+      <c r="D73" t="s">
+        <v>163</v>
+      </c>
+      <c r="E73" t="s">
+        <v>26</v>
+      </c>
+      <c r="F73" t="s">
+        <v>165</v>
+      </c>
+      <c r="G73" t="s">
+        <v>166</v>
+      </c>
+      <c r="H73" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" t="s">
+        <v>167</v>
+      </c>
+      <c r="D74" t="s">
+        <v>168</v>
+      </c>
+      <c r="E74" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" t="s">
+        <v>4</v>
+      </c>
+      <c r="G74" t="s">
+        <v>4</v>
+      </c>
+      <c r="H74" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>167</v>
+      </c>
+      <c r="D75" t="s">
+        <v>168</v>
+      </c>
+      <c r="E75" t="s">
+        <v>26</v>
+      </c>
+      <c r="F75" t="s">
+        <v>170</v>
+      </c>
+      <c r="G75" t="s">
+        <v>171</v>
+      </c>
+      <c r="H75" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>172</v>
+      </c>
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" t="s">
+        <v>173</v>
+      </c>
+      <c r="E76" t="s">
+        <v>174</v>
+      </c>
+      <c r="F76" t="s">
+        <v>4</v>
+      </c>
+      <c r="G76" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C77" t="s">
+        <v>176</v>
+      </c>
+      <c r="D77" t="s">
+        <v>177</v>
+      </c>
+      <c r="E77" t="s">
+        <v>3</v>
+      </c>
+      <c r="F77" t="s">
+        <v>4</v>
+      </c>
+      <c r="G77" t="s">
+        <v>4</v>
+      </c>
+      <c r="H77" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" t="s">
+        <v>179</v>
+      </c>
+      <c r="D78" t="s">
+        <v>180</v>
+      </c>
+      <c r="E78" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78" t="s">
+        <v>181</v>
+      </c>
+      <c r="G78" t="s">
+        <v>182</v>
+      </c>
+      <c r="H78" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>172</v>
+      </c>
+      <c r="C79" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" t="s">
+        <v>183</v>
+      </c>
+      <c r="E79" t="s">
+        <v>174</v>
+      </c>
+      <c r="F79" t="s">
+        <v>4</v>
+      </c>
+      <c r="G79" t="s">
+        <v>4</v>
+      </c>
+      <c r="H79" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" t="s">
+        <v>184</v>
+      </c>
+      <c r="D80" t="s">
+        <v>185</v>
+      </c>
+      <c r="E80" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
+        <v>4</v>
+      </c>
+      <c r="G80" t="s">
+        <v>4</v>
+      </c>
+      <c r="H80" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>184</v>
+      </c>
+      <c r="D81" t="s">
+        <v>185</v>
+      </c>
+      <c r="E81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F81" t="s">
+        <v>187</v>
+      </c>
+      <c r="G81" t="s">
+        <v>188</v>
+      </c>
+      <c r="H81" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" t="s">
+        <v>190</v>
+      </c>
+      <c r="E82" t="s">
+        <v>191</v>
+      </c>
+      <c r="F82" t="s">
+        <v>4</v>
+      </c>
+      <c r="G82" t="s">
+        <v>4</v>
+      </c>
+      <c r="H82" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B83" t="s">
+        <v>0</v>
+      </c>
+      <c r="C83" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" t="s">
+        <v>203</v>
+      </c>
+      <c r="E83" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" t="s">
+        <v>204</v>
+      </c>
+      <c r="I83" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>206</v>
+      </c>
+      <c r="D84" t="s">
+        <v>203</v>
+      </c>
+      <c r="E84" t="s">
+        <v>26</v>
+      </c>
+      <c r="F84" t="s">
+        <v>207</v>
+      </c>
+      <c r="G84" t="s">
+        <v>208</v>
+      </c>
+      <c r="H84" t="s">
+        <v>204</v>
+      </c>
+      <c r="I84" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84.0</v>
+      </c>
+      <c r="B85" t="s">
+        <v>207</v>
+      </c>
+      <c r="C85" t="s">
+        <v>204</v>
+      </c>
+      <c r="D85" t="s">
+        <v>209</v>
+      </c>
+      <c r="E85" t="s">
+        <v>207</v>
+      </c>
+      <c r="F85" t="s">
+        <v>207</v>
+      </c>
+      <c r="G85" t="s">
+        <v>210</v>
+      </c>
+      <c r="H85" t="s">
+        <v>204</v>
+      </c>
+      <c r="I85" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85.0</v>
+      </c>
+      <c r="B86" t="s">
+        <v>0</v>
+      </c>
+      <c r="C86" t="s">
+        <v>211</v>
+      </c>
+      <c r="D86" t="s">
+        <v>212</v>
+      </c>
+      <c r="E86" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" t="s">
+        <v>4</v>
+      </c>
+      <c r="G86" t="s">
+        <v>4</v>
+      </c>
+      <c r="H86" t="s">
+        <v>213</v>
+      </c>
+      <c r="I86" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="B87" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" t="s">
+        <v>214</v>
+      </c>
+      <c r="D87" t="s">
+        <v>212</v>
+      </c>
+      <c r="E87" t="s">
+        <v>26</v>
+      </c>
+      <c r="F87" t="s">
+        <v>215</v>
+      </c>
+      <c r="G87" t="s">
+        <v>216</v>
+      </c>
+      <c r="H87" t="s">
+        <v>213</v>
+      </c>
+      <c r="I87" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87.0</v>
+      </c>
+      <c r="B88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C88" t="s">
+        <v>217</v>
+      </c>
+      <c r="D88" t="s">
+        <v>218</v>
+      </c>
+      <c r="E88" t="s">
+        <v>3</v>
+      </c>
+      <c r="F88" t="s">
+        <v>4</v>
+      </c>
+      <c r="G88" t="s">
+        <v>4</v>
+      </c>
+      <c r="H88" t="s">
+        <v>219</v>
+      </c>
+      <c r="I88" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="B89" t="s">
+        <v>24</v>
+      </c>
+      <c r="C89" t="s">
+        <v>217</v>
+      </c>
+      <c r="D89" t="s">
+        <v>218</v>
+      </c>
+      <c r="E89" t="s">
+        <v>26</v>
+      </c>
+      <c r="F89" t="s">
+        <v>220</v>
+      </c>
+      <c r="G89" t="s">
+        <v>221</v>
+      </c>
+      <c r="H89" t="s">
+        <v>219</v>
+      </c>
+      <c r="I89" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89.0</v>
+      </c>
+      <c r="B90" t="s">
+        <v>172</v>
+      </c>
+      <c r="C90" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" t="s">
+        <v>222</v>
+      </c>
+      <c r="E90" t="s">
+        <v>191</v>
+      </c>
+      <c r="F90" t="s">
+        <v>4</v>
+      </c>
+      <c r="G90" t="s">
+        <v>4</v>
+      </c>
+      <c r="H90" t="s">
+        <v>4</v>
+      </c>
+      <c r="I90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="B91" t="s">
+        <v>0</v>
+      </c>
+      <c r="C91" t="s">
+        <v>224</v>
+      </c>
+      <c r="D91" t="s">
+        <v>225</v>
+      </c>
+      <c r="E91" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" t="s">
+        <v>226</v>
+      </c>
+      <c r="I91" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91.0</v>
+      </c>
+      <c r="B92" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" t="s">
+        <v>224</v>
+      </c>
+      <c r="D92" t="s">
+        <v>225</v>
+      </c>
+      <c r="E92" t="s">
+        <v>26</v>
+      </c>
+      <c r="F92" t="s">
+        <v>227</v>
+      </c>
+      <c r="G92" t="s">
+        <v>228</v>
+      </c>
+      <c r="H92" t="s">
+        <v>226</v>
+      </c>
+      <c r="I92" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92.0</v>
+      </c>
+      <c r="B93" t="s">
+        <v>172</v>
+      </c>
+      <c r="C93" t="s">
+        <v>4</v>
+      </c>
+      <c r="D93" t="s">
+        <v>229</v>
+      </c>
+      <c r="E93" t="s">
+        <v>191</v>
+      </c>
+      <c r="F93" t="s">
+        <v>4</v>
+      </c>
+      <c r="G93" t="s">
+        <v>4</v>
+      </c>
+      <c r="H93" t="s">
+        <v>4</v>
+      </c>
+      <c r="I93" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93.0</v>
+      </c>
+      <c r="B94" t="s">
+        <v>0</v>
+      </c>
+      <c r="C94" t="s">
+        <v>230</v>
+      </c>
+      <c r="D94" t="s">
+        <v>231</v>
+      </c>
+      <c r="E94" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" t="s">
+        <v>232</v>
+      </c>
+      <c r="I94" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94.0</v>
+      </c>
+      <c r="B95" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" t="s">
+        <v>230</v>
+      </c>
+      <c r="D95" t="s">
+        <v>231</v>
+      </c>
+      <c r="E95" t="s">
+        <v>26</v>
+      </c>
+      <c r="F95" t="s">
+        <v>233</v>
+      </c>
+      <c r="G95" t="s">
+        <v>234</v>
+      </c>
+      <c r="H95" t="s">
+        <v>232</v>
+      </c>
+      <c r="I95" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="B96" t="s">
+        <v>0</v>
+      </c>
+      <c r="C96" t="s">
+        <v>235</v>
+      </c>
+      <c r="D96" t="s">
+        <v>236</v>
+      </c>
+      <c r="E96" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" t="s">
+        <v>237</v>
+      </c>
+      <c r="I96" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96.0</v>
+      </c>
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" t="s">
+        <v>235</v>
+      </c>
+      <c r="D97" t="s">
+        <v>236</v>
+      </c>
+      <c r="E97" t="s">
+        <v>26</v>
+      </c>
+      <c r="F97" t="s">
+        <v>238</v>
+      </c>
+      <c r="G97" t="s">
+        <v>239</v>
+      </c>
+      <c r="H97" t="s">
+        <v>237</v>
+      </c>
+      <c r="I97" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97.0</v>
+      </c>
+      <c r="B98" t="s">
+        <v>238</v>
+      </c>
+      <c r="C98" t="s">
+        <v>237</v>
+      </c>
+      <c r="D98" t="s">
+        <v>240</v>
+      </c>
+      <c r="E98" t="s">
+        <v>238</v>
+      </c>
+      <c r="F98" t="s">
+        <v>238</v>
+      </c>
+      <c r="G98" t="s">
+        <v>241</v>
+      </c>
+      <c r="H98" t="s">
+        <v>237</v>
+      </c>
+      <c r="I98" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98.0</v>
+      </c>
+      <c r="B99" t="s">
+        <v>0</v>
+      </c>
+      <c r="C99" t="s">
+        <v>242</v>
+      </c>
+      <c r="D99" t="s">
+        <v>243</v>
+      </c>
+      <c r="E99" t="s">
+        <v>3</v>
+      </c>
+      <c r="F99" t="s">
+        <v>4</v>
+      </c>
+      <c r="G99" t="s">
+        <v>4</v>
+      </c>
+      <c r="H99" t="s">
+        <v>244</v>
+      </c>
+      <c r="I99" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="B100" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" t="s">
+        <v>245</v>
+      </c>
+      <c r="D100" t="s">
+        <v>243</v>
+      </c>
+      <c r="E100" t="s">
+        <v>26</v>
+      </c>
+      <c r="F100" t="s">
+        <v>246</v>
+      </c>
+      <c r="G100" t="s">
+        <v>247</v>
+      </c>
+      <c r="H100" t="s">
+        <v>244</v>
+      </c>
+      <c r="I100" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="B101" t="s">
+        <v>246</v>
+      </c>
+      <c r="C101" t="s">
+        <v>244</v>
+      </c>
+      <c r="D101" t="s">
+        <v>248</v>
+      </c>
+      <c r="E101" t="s">
+        <v>246</v>
+      </c>
+      <c r="F101" t="s">
+        <v>246</v>
+      </c>
+      <c r="G101" t="s">
+        <v>249</v>
+      </c>
+      <c r="H101" t="s">
+        <v>244</v>
+      </c>
+      <c r="I101" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
